--- a/data/trans_orig/IP18B-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP18B-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>607</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5697</t>
+          <t>5533</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3815</t>
+          <t>4390</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1501</t>
+          <t>1326</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7391</t>
+          <t>7467</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,55%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>93947</t>
+          <t>93499</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>100020</t>
+          <t>100047</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>98489</t>
+          <t>99060</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>106227</t>
+          <t>106367</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,88%</t>
+          <t>91,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>195840</t>
+          <t>195662</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>204942</t>
+          <t>205036</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>93,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,6%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>591</t>
+          <t>597</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5172</t>
+          <t>5046</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1299</t>
+          <t>1294</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7942</t>
+          <t>7370</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2544</t>
+          <t>2540</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>10484</t>
+          <t>9832</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,68%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6392</t>
+          <t>6229</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>17253</t>
+          <t>17365</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>5642</t>
+          <t>5589</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>15894</t>
+          <t>15412</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>14575</t>
+          <t>14753</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>29586</t>
+          <t>28891</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,2%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>202371</t>
+          <t>203382</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>217100</t>
+          <t>217625</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>87,14%</t>
+          <t>87,58%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>203162</t>
+          <t>203223</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>217778</t>
+          <t>217813</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>86,78%</t>
+          <t>86,81%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>409805</t>
+          <t>410585</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>431446</t>
+          <t>431148</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>87,88%</t>
+          <t>88,05%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,45%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5739</t>
+          <t>6259</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16584</t>
+          <t>17298</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8439</t>
+          <t>8165</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20074</t>
+          <t>19656</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>16838</t>
+          <t>16989</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>32865</t>
+          <t>31948</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>6,85%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5111</t>
+          <t>4984</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>14575</t>
+          <t>14181</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4450</t>
+          <t>4147</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>13333</t>
+          <t>13782</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>11607</t>
+          <t>11265</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>24805</t>
+          <t>23585</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>10,61%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>70540</t>
+          <t>70269</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>84982</t>
+          <t>84375</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>66,53%</t>
+          <t>66,27%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>80,15%</t>
+          <t>79,58%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>82514</t>
+          <t>82723</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>96599</t>
+          <t>96577</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>70,97%</t>
+          <t>71,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>83,08%</t>
+          <t>83,06%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>155902</t>
+          <t>158595</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>177470</t>
+          <t>179002</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>70,13%</t>
+          <t>71,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>79,83%</t>
+          <t>80,52%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>13424</t>
+          <t>13459</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>26060</t>
+          <t>26360</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>12689</t>
+          <t>12499</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>25131</t>
+          <t>25091</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>28598</t>
+          <t>29228</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>46901</t>
+          <t>46890</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>21,09%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8778</t>
+          <t>8779</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21090</t>
+          <t>21062</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10070</t>
+          <t>9957</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>22223</t>
+          <t>22039</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>22150</t>
+          <t>21606</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>38084</t>
+          <t>38271</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,74%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>50348</t>
+          <t>51241</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>70700</t>
+          <t>71096</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>32,29%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>44,55%</t>
+          <t>44,8%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>54577</t>
+          <t>54011</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>74613</t>
+          <t>73685</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>32,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>44,61%</t>
+          <t>44,05%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>111095</t>
+          <t>111248</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>138943</t>
+          <t>140152</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>34,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>42,63%</t>
+          <t>43,0%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>73621</t>
+          <t>74262</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>94200</t>
+          <t>94699</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>46,39%</t>
+          <t>46,8%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>59,36%</t>
+          <t>59,68%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>76644</t>
+          <t>77536</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>98249</t>
+          <t>98369</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>45,82%</t>
+          <t>46,36%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>58,74%</t>
+          <t>58,81%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>157534</t>
+          <t>155252</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>186766</t>
+          <t>184847</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>48,33%</t>
+          <t>47,63%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>57,3%</t>
+          <t>56,71%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>26487</t>
+          <t>27068</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>44683</t>
+          <t>45931</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>26671</t>
+          <t>25496</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>44963</t>
+          <t>44729</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>57599</t>
+          <t>58166</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>83626</t>
+          <t>84562</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,9%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>429210</t>
+          <t>429125</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>464163</t>
+          <t>462620</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>71,7%</t>
+          <t>71,68%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>77,53%</t>
+          <t>77,28%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>452444</t>
+          <t>450040</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>484936</t>
+          <t>486568</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>72,27%</t>
+          <t>71,89%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>77,46%</t>
+          <t>77,73%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>891477</t>
+          <t>889736</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>940898</t>
+          <t>941094</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>72,79%</t>
+          <t>72,65%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>76,83%</t>
+          <t>76,84%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>100459</t>
+          <t>100758</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>132024</t>
+          <t>131838</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>107051</t>
+          <t>106322</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>138754</t>
+          <t>138219</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>215314</t>
+          <t>215505</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>262744</t>
+          <t>260096</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>21,24%</t>
         </is>
       </c>
     </row>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>481</t>
+          <t>474</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5128</t>
+          <t>4753</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>635</t>
+          <t>643</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5744</t>
+          <t>5969</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1598</t>
+          <t>1752</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8252</t>
+          <t>9085</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,18%</t>
         </is>
       </c>
     </row>
@@ -3358,12 +3358,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>133263</t>
+          <t>133673</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>140344</t>
+          <t>140390</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3373,12 +3373,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3393,12 +3393,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>137101</t>
+          <t>137085</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>143247</t>
+          <t>143095</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3408,12 +3408,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3428,12 +3428,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>273922</t>
+          <t>273685</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>282271</t>
+          <t>282447</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3443,12 +3443,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,74%</t>
         </is>
       </c>
     </row>
@@ -3471,12 +3471,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>587</t>
+          <t>586</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5862</t>
+          <t>6012</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3299</t>
+          <t>3555</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3526,7 +3526,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3541,12 +3541,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1147</t>
+          <t>1153</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>6898</t>
+          <t>6838</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3561,7 +3561,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,39%</t>
         </is>
       </c>
     </row>
@@ -3701,12 +3701,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5882</t>
+          <t>5800</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>16151</t>
+          <t>16491</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3716,12 +3716,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>12020</t>
+          <t>11463</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>25903</t>
+          <t>25223</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3751,12 +3751,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>20328</t>
+          <t>19554</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>38038</t>
+          <t>38162</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3786,12 +3786,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,93%</t>
         </is>
       </c>
     </row>
@@ -3814,12 +3814,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>184027</t>
+          <t>182868</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>201177</t>
+          <t>201630</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3829,12 +3829,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>82,46%</t>
+          <t>81,94%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>90,35%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>216598</t>
+          <t>215304</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>234733</t>
+          <t>233968</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3864,12 +3864,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>84,01%</t>
+          <t>83,51%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>91,04%</t>
+          <t>90,75%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>405514</t>
+          <t>405874</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>430921</t>
+          <t>429829</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3899,12 +3899,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>84,31%</t>
+          <t>84,38%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>89,59%</t>
+          <t>89,36%</t>
         </is>
       </c>
     </row>
@@ -3927,12 +3927,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13212</t>
+          <t>13374</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>27800</t>
+          <t>28911</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3942,12 +3942,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8594</t>
+          <t>8817</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21599</t>
+          <t>21189</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3977,12 +3977,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>25454</t>
+          <t>25821</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>45737</t>
+          <t>45438</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4012,12 +4012,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,45%</t>
         </is>
       </c>
     </row>
@@ -4157,12 +4157,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6355</t>
+          <t>6692</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>17667</t>
+          <t>16711</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4172,12 +4172,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7273</t>
+          <t>7151</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>19599</t>
+          <t>19953</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4207,12 +4207,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>16404</t>
+          <t>15522</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>31529</t>
+          <t>30988</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4242,12 +4242,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,25%</t>
         </is>
       </c>
     </row>
@@ -4270,12 +4270,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>117297</t>
+          <t>117308</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>132969</t>
+          <t>132393</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>77,61%</t>
+          <t>77,62%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>87,98%</t>
+          <t>87,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>109662</t>
+          <t>110023</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>126438</t>
+          <t>127384</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4320,12 +4320,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>72,54%</t>
+          <t>72,77%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>83,63%</t>
+          <t>84,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>233589</t>
+          <t>232449</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>255700</t>
+          <t>256743</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4355,12 +4355,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>77,27%</t>
+          <t>76,89%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>84,58%</t>
+          <t>84,93%</t>
         </is>
       </c>
     </row>
@@ -4383,12 +4383,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>8645</t>
+          <t>8941</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>21305</t>
+          <t>20902</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4398,12 +4398,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>14534</t>
+          <t>13566</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>27685</t>
+          <t>27108</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>25583</t>
+          <t>25417</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>43947</t>
+          <t>44370</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,68%</t>
         </is>
       </c>
     </row>
@@ -4613,12 +4613,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7085</t>
+          <t>7368</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18719</t>
+          <t>18314</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13356</t>
+          <t>12970</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>26256</t>
+          <t>25755</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>22887</t>
+          <t>22549</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>39367</t>
+          <t>40570</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4698,12 +4698,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,73%</t>
         </is>
       </c>
     </row>
@@ -4726,12 +4726,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>60233</t>
+          <t>59572</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>80856</t>
+          <t>80874</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4741,12 +4741,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>39,07%</t>
+          <t>38,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>52,45%</t>
+          <t>52,46%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>59178</t>
+          <t>59136</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>79151</t>
+          <t>78956</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>35,95%</t>
+          <t>35,93%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>48,09%</t>
+          <t>47,97%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>124343</t>
+          <t>124697</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>153090</t>
+          <t>154496</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>39,01%</t>
+          <t>39,12%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>48,03%</t>
+          <t>48,47%</t>
         </is>
       </c>
     </row>
@@ -4839,12 +4839,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>61612</t>
+          <t>61294</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>83124</t>
+          <t>82683</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4854,12 +4854,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>39,97%</t>
+          <t>39,76%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>53,92%</t>
+          <t>53,63%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>66416</t>
+          <t>66784</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>87206</t>
+          <t>86921</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>40,35%</t>
+          <t>40,58%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>52,98%</t>
+          <t>52,81%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>134696</t>
+          <t>134370</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>164437</t>
+          <t>164515</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>42,26%</t>
+          <t>42,15%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>51,59%</t>
+          <t>51,61%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>26031</t>
+          <t>26679</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>44964</t>
+          <t>45399</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>40346</t>
+          <t>39674</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>62412</t>
+          <t>62672</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>71474</t>
+          <t>71668</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>100599</t>
+          <t>100686</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5154,7 +5154,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -5182,12 +5182,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>507738</t>
+          <t>510554</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>543449</t>
+          <t>545942</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>75,71%</t>
+          <t>76,13%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>81,04%</t>
+          <t>81,41%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>535959</t>
+          <t>534989</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>574154</t>
+          <t>573493</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>74,7%</t>
+          <t>74,56%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>80,02%</t>
+          <t>79,93%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5252,12 +5252,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1057224</t>
+          <t>1056504</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1108670</t>
+          <t>1106926</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>76,16%</t>
+          <t>76,11%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>79,87%</t>
+          <t>79,74%</t>
         </is>
       </c>
     </row>
@@ -5295,12 +5295,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>92957</t>
+          <t>92977</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>126240</t>
+          <t>125513</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5315,7 +5315,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>96195</t>
+          <t>95324</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>126511</t>
+          <t>129567</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5365,12 +5365,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>196712</t>
+          <t>200046</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>241298</t>
+          <t>244351</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5380,12 +5380,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,6%</t>
         </is>
       </c>
     </row>
@@ -5762,7 +5762,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4737</t>
+          <t>4384</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5777,7 +5777,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5797,7 +5797,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>4485</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5812,7 +5812,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5827,12 +5827,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>772</t>
+          <t>624</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6986</t>
+          <t>6527</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5842,12 +5842,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,65%</t>
         </is>
       </c>
     </row>
@@ -5870,12 +5870,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>117890</t>
+          <t>118386</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>125402</t>
+          <t>125458</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5905,12 +5905,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>100586</t>
+          <t>100595</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>111433</t>
+          <t>111287</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,96%</t>
+          <t>84,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>94,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>221865</t>
+          <t>222165</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>234984</t>
+          <t>235053</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>90,36%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,6%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1254</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7605</t>
+          <t>7248</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6103</t>
+          <t>6048</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>17188</t>
+          <t>16241</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>8700</t>
+          <t>8765</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>20371</t>
+          <t>20669</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,41%</t>
         </is>
       </c>
     </row>
@@ -6213,12 +6213,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6045</t>
+          <t>5992</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>16758</t>
+          <t>17024</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6228,12 +6228,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6248,12 +6248,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3889</t>
+          <t>3893</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>12984</t>
+          <t>12056</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6268,7 +6268,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6283,12 +6283,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>11635</t>
+          <t>11579</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>24948</t>
+          <t>25453</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,87%</t>
         </is>
       </c>
     </row>
@@ -6326,12 +6326,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>156996</t>
+          <t>156987</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>172848</t>
+          <t>174188</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6346,7 +6346,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>88,06%</t>
+          <t>88,74%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>189009</t>
+          <t>188690</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>207723</t>
+          <t>206954</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>79,54%</t>
+          <t>79,41%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>87,42%</t>
+          <t>87,09%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>351922</t>
+          <t>352709</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>375361</t>
+          <t>376653</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>81,1%</t>
+          <t>81,28%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>86,51%</t>
+          <t>86,8%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14446</t>
+          <t>12841</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>27312</t>
+          <t>26551</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>22736</t>
+          <t>24022</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>40547</t>
+          <t>41157</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>41801</t>
+          <t>41135</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>63215</t>
+          <t>63024</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,52%</t>
         </is>
       </c>
     </row>
@@ -6669,12 +6669,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6610</t>
+          <t>6787</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>17387</t>
+          <t>16543</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6684,12 +6684,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5501</t>
+          <t>5262</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>15943</t>
+          <t>14890</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>14035</t>
+          <t>13507</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>28454</t>
+          <t>28255</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,28%</t>
         </is>
       </c>
     </row>
@@ -6782,12 +6782,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>116060</t>
+          <t>115681</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>135027</t>
+          <t>135479</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>67,53%</t>
+          <t>67,31%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>78,57%</t>
+          <t>78,83%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>119184</t>
+          <t>119079</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>138405</t>
+          <t>138757</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6832,12 +6832,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>70,35%</t>
+          <t>70,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>81,7%</t>
+          <t>81,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>241595</t>
+          <t>241483</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>268546</t>
+          <t>267540</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>70,79%</t>
+          <t>70,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>78,69%</t>
+          <t>78,4%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>26802</t>
+          <t>26567</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>44833</t>
+          <t>44920</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>22525</t>
+          <t>22687</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>39670</t>
+          <t>40378</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>53435</t>
+          <t>54043</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>77500</t>
+          <t>78833</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>23,1%</t>
         </is>
       </c>
     </row>
@@ -7125,12 +7125,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3731</t>
+          <t>3843</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11989</t>
+          <t>12188</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7140,12 +7140,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>16163</t>
+          <t>16032</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>31101</t>
+          <t>31275</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7175,12 +7175,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>21238</t>
+          <t>22141</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>39117</t>
+          <t>40033</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7210,12 +7210,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>13,2%</t>
         </is>
       </c>
     </row>
@@ -7238,12 +7238,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>57763</t>
+          <t>58851</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>79106</t>
+          <t>78581</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7253,12 +7253,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>37,74%</t>
+          <t>38,45%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>51,68%</t>
+          <t>51,34%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7273,12 +7273,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>51004</t>
+          <t>49855</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>70968</t>
+          <t>71009</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>33,96%</t>
+          <t>33,2%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>47,26%</t>
+          <t>47,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7308,12 +7308,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>112909</t>
+          <t>114968</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>142499</t>
+          <t>144021</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7323,12 +7323,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>37,23%</t>
+          <t>37,91%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>46,99%</t>
+          <t>47,49%</t>
         </is>
       </c>
     </row>
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>68031</t>
+          <t>66965</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>88305</t>
+          <t>87154</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>44,45%</t>
+          <t>43,75%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>57,69%</t>
+          <t>56,94%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>56282</t>
+          <t>57185</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>77371</t>
+          <t>78817</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>37,48%</t>
+          <t>38,08%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>51,52%</t>
+          <t>52,48%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7421,12 +7421,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>129365</t>
+          <t>129724</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>159128</t>
+          <t>159138</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7436,7 +7436,7 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>42,66%</t>
+          <t>42,78%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -7581,12 +7581,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>21205</t>
+          <t>22215</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>39404</t>
+          <t>39758</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7596,12 +7596,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7616,12 +7616,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>30280</t>
+          <t>31493</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>52061</t>
+          <t>53121</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7631,12 +7631,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>57203</t>
+          <t>57679</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>84244</t>
+          <t>84218</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7666,7 +7666,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -7694,12 +7694,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>463851</t>
+          <t>463582</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>501824</t>
+          <t>499803</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7709,12 +7709,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>71,51%</t>
+          <t>71,46%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>77,36%</t>
+          <t>77,05%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7729,12 +7729,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>476442</t>
+          <t>475281</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>514206</t>
+          <t>514934</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7744,12 +7744,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>70,52%</t>
+          <t>70,35%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>76,11%</t>
+          <t>76,22%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7764,12 +7764,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>948962</t>
+          <t>952048</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1004038</t>
+          <t>1003988</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7779,12 +7779,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>71,66%</t>
+          <t>71,89%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>75,82%</t>
+          <t>75,81%</t>
         </is>
       </c>
     </row>
@@ -7807,12 +7807,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>118194</t>
+          <t>119075</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>153281</t>
+          <t>152959</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>121365</t>
+          <t>122331</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>157614</t>
+          <t>158757</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>251289</t>
+          <t>251407</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>300680</t>
+          <t>299076</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7897,7 +7897,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>22,58%</t>
         </is>
       </c>
     </row>
@@ -8417,7 +8417,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16900</t>
+          <t>16671</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -8432,7 +8432,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,62%</t>
+          <t>90,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -8452,7 +8452,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>32696</t>
+          <t>33163</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -8467,7 +8467,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -8535,7 +8535,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1547</t>
+          <t>1776</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8550,7 +8550,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8570,7 +8570,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>2046</t>
+          <t>1579</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8585,7 +8585,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>4,54%</t>
         </is>
       </c>
     </row>
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>798</t>
+          <t>754</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5975</t>
+          <t>5771</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8760,12 +8760,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>611</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>6929</t>
+          <t>6502</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8775,12 +8775,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8795,12 +8795,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>2036</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>9600</t>
+          <t>9261</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8810,12 +8810,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>14,96%</t>
         </is>
       </c>
     </row>
@@ -8838,12 +8838,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>20849</t>
+          <t>20770</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>26731</t>
+          <t>26549</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8853,12 +8853,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>73,94%</t>
+          <t>73,66%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8873,12 +8873,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>23692</t>
+          <t>23697</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>31457</t>
+          <t>31378</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8888,12 +8888,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>70,24%</t>
+          <t>70,26%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>93,03%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8908,12 +8908,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>46856</t>
+          <t>47449</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>56256</t>
+          <t>56922</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8923,12 +8923,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>75,67%</t>
+          <t>76,62%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>90,85%</t>
+          <t>91,92%</t>
         </is>
       </c>
     </row>
@@ -8956,7 +8956,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4220</t>
+          <t>4072</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8971,7 +8971,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8986,12 +8986,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>665</t>
+          <t>693</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6609</t>
+          <t>7111</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9001,12 +9001,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9021,12 +9021,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1815</t>
+          <t>1751</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8470</t>
+          <t>8642</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9036,12 +9036,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,96%</t>
         </is>
       </c>
     </row>
@@ -9181,12 +9181,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1060</t>
+          <t>866</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7520</t>
+          <t>8387</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9196,12 +9196,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9216,12 +9216,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1675</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>9448</t>
+          <t>8894</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9231,12 +9231,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9251,12 +9251,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3894</t>
+          <t>3805</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>13261</t>
+          <t>13873</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9266,12 +9266,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>20,35%</t>
         </is>
       </c>
     </row>
@@ -9294,12 +9294,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>21667</t>
+          <t>21569</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>29309</t>
+          <t>29456</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9309,12 +9309,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>69,23%</t>
+          <t>68,92%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>94,12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9329,12 +9329,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23032</t>
+          <t>22886</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>32455</t>
+          <t>32690</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9344,12 +9344,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>62,47%</t>
+          <t>62,07%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>88,02%</t>
+          <t>88,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9364,12 +9364,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>47833</t>
+          <t>47765</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>60247</t>
+          <t>60549</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9379,12 +9379,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>70,17%</t>
+          <t>70,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>88,38%</t>
+          <t>88,82%</t>
         </is>
       </c>
     </row>
@@ -9412,7 +9412,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5285</t>
+          <t>5603</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9427,7 +9427,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9442,12 +9442,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1662</t>
+          <t>1305</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>9503</t>
+          <t>8882</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9457,12 +9457,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9477,12 +9477,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2473</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>10967</t>
+          <t>11035</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9492,12 +9492,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>16,19%</t>
         </is>
       </c>
     </row>
@@ -9637,12 +9637,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2835</t>
+          <t>3065</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9973</t>
+          <t>10337</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>40,66%</t>
+          <t>42,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2828</t>
+          <t>2920</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10952</t>
+          <t>10799</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9707,12 +9707,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7572</t>
+          <t>7445</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>18490</t>
+          <t>18520</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9722,12 +9722,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>27,61%</t>
         </is>
       </c>
     </row>
@@ -9750,12 +9750,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7648</t>
+          <t>6787</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>15755</t>
+          <t>15265</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9765,12 +9765,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>27,67%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>64,24%</t>
+          <t>62,24%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9785,12 +9785,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>14911</t>
+          <t>14875</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>27385</t>
+          <t>26597</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9800,12 +9800,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>35,05%</t>
+          <t>34,96%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>64,36%</t>
+          <t>62,51%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9820,12 +9820,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>25253</t>
+          <t>24935</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>40047</t>
+          <t>39767</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9835,12 +9835,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>37,65%</t>
+          <t>37,18%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>59,71%</t>
+          <t>59,29%</t>
         </is>
       </c>
     </row>
@@ -9863,12 +9863,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3916</t>
+          <t>4017</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>11189</t>
+          <t>11101</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9878,12 +9878,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>45,62%</t>
+          <t>45,26%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9898,12 +9898,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>9759</t>
+          <t>9757</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>22409</t>
+          <t>21602</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>52,67%</t>
+          <t>50,77%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9933,12 +9933,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>15700</t>
+          <t>15846</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>30822</t>
+          <t>30820</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9948,7 +9948,7 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>23,63%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -10093,12 +10093,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>7095</t>
+          <t>7330</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>17965</t>
+          <t>18001</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>8700</t>
+          <t>7637</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>20784</t>
+          <t>20142</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10163,12 +10163,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>17084</t>
+          <t>18026</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>33511</t>
+          <t>33082</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10178,12 +10178,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,27%</t>
         </is>
       </c>
     </row>
@@ -10206,12 +10206,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>70726</t>
+          <t>71288</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>84759</t>
+          <t>84744</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10221,12 +10221,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>70,5%</t>
+          <t>71,06%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>84,49%</t>
+          <t>84,48%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>85091</t>
+          <t>84853</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>104228</t>
+          <t>104410</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>64,66%</t>
+          <t>64,48%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>79,21%</t>
+          <t>79,34%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10276,12 +10276,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>161722</t>
+          <t>162218</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>186303</t>
+          <t>185488</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10291,12 +10291,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>69,74%</t>
+          <t>69,95%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>80,34%</t>
+          <t>79,98%</t>
         </is>
       </c>
     </row>
@@ -10319,12 +10319,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6111</t>
+          <t>5958</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>16241</t>
+          <t>16520</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10334,12 +10334,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>15913</t>
+          <t>15061</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>32454</t>
+          <t>33374</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10389,12 +10389,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>24196</t>
+          <t>24229</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>44452</t>
+          <t>43879</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10404,12 +10404,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>18,92%</t>
         </is>
       </c>
     </row>
